--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-01-25T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -345,6 +345,12 @@
     <t>Value of extension</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSTipoOtroTelefono</t>
+  </si>
+  <si>
     <t>Extension.value[x].id</t>
   </si>
   <si>
@@ -448,12 +454,6 @@
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSTipoOtroTelefono</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1551,13 +1551,11 @@
         <v>71</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X7" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="X7" s="2"/>
       <c r="Y7" t="s" s="2">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="Z7" t="s" s="2">
         <v>71</v>
@@ -1595,7 +1593,7 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -1695,11 +1693,11 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -1721,13 +1719,13 @@
         <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
@@ -1797,7 +1795,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -1820,19 +1818,19 @@
         <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O10" t="s" s="2">
         <v>71</v>
@@ -1881,7 +1879,7 @@
         <v>71</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>72</v>
@@ -1896,12 +1894,12 @@
         <v>103</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2001,11 +1999,11 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -2027,13 +2025,13 @@
         <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -2103,7 +2101,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2129,16 +2127,16 @@
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O13" t="s" s="2">
         <v>71</v>
@@ -2187,7 +2185,7 @@
         <v>71</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>72</v>
@@ -2202,12 +2200,12 @@
         <v>103</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2233,13 +2231,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
@@ -2289,7 +2287,7 @@
         <v>71</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>72</v>
@@ -2304,12 +2302,12 @@
         <v>103</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2332,17 +2330,17 @@
         <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>71</v>
@@ -2367,11 +2365,13 @@
         <v>71</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="X15" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="Y15" t="s" s="2">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>71</v>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TipoOtroTelefono.xlsx
+++ b/StructureDefinition-TipoOtroTelefono.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
